--- a/utils/monday_sprint_sprint_2023-10.xlsx
+++ b/utils/monday_sprint_sprint_2023-10.xlsx
@@ -225,7 +225,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Abril</t>
@@ -2743,7 +2743,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
@@ -2763,7 +2763,7 @@
         <v>24</v>
       </c>
       <c r="Q13">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
@@ -2831,7 +2831,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>65</v>

--- a/utils/monday_sprint_sprint_2023-10.xlsx
+++ b/utils/monday_sprint_sprint_2023-10.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="154">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>19207</t>
+    <t>4157217188</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>16/03/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>17/05/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>19379</t>
+    <t>4198314104</t>
   </si>
   <si>
     <t>Alteração em massa de TAGs</t>
@@ -111,10 +111,13 @@
     <t>24/03/2023</t>
   </si>
   <si>
+    <t>19/05/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>19203</t>
+    <t>4271583390</t>
   </si>
   <si>
     <t>Corrigir Tipo de OTF - QVIEW</t>
@@ -123,18 +126,24 @@
     <t>06/04/2023</t>
   </si>
   <si>
+    <t>21/05/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>19485</t>
+    <t>4271754529</t>
   </si>
   <si>
     <t>Sistema de inventário em dispositivo móvel</t>
   </si>
   <si>
+    <t>16/05/2023</t>
+  </si>
+  <si>
     <t>4436569930</t>
   </si>
   <si>
@@ -156,7 +165,7 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>20041</t>
+    <t>4408813609</t>
   </si>
   <si>
     <t>Movimentação de Estorno PCP</t>
@@ -168,7 +177,10 @@
     <t>03/05/2023</t>
   </si>
   <si>
-    <t>20006</t>
+    <t>20/05/2023</t>
+  </si>
+  <si>
+    <t>4426385788</t>
   </si>
   <si>
     <t>Falta de informação na OTF</t>
@@ -177,7 +189,7 @@
     <t>05/05/2023</t>
   </si>
   <si>
-    <t>20007</t>
+    <t>4426519856</t>
   </si>
   <si>
     <t>Alteração dos Fluxos</t>
@@ -186,64 +198,76 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>19927</t>
+    <t>4436633630</t>
   </si>
   <si>
     <t>Layout de tela para o gestão a vista da desmoldagem - Criar Tema</t>
   </si>
   <si>
+    <t>18/05/2023</t>
+  </si>
+  <si>
+    <t>4436640041</t>
+  </si>
+  <si>
     <t>Layout de tela para o gestão a vista da desmoldagem - Revisar KB</t>
   </si>
   <si>
+    <t>15/05/2023</t>
+  </si>
+  <si>
+    <t>4436658258</t>
+  </si>
+  <si>
     <t>Layout de tela para o gestão a vista da desmoldagem - Tela de solicitação de caixa</t>
   </si>
   <si>
+    <t>4436650888</t>
+  </si>
+  <si>
     <t>Layout de tela para o gestão a vista da desmoldagem -</t>
   </si>
   <si>
-    <t>19926</t>
+    <t>4427072014</t>
   </si>
   <si>
     <t>Relatório e tempos da desmoldagem</t>
   </si>
   <si>
-    <t>20235</t>
+    <t>11/05/2023</t>
+  </si>
+  <si>
+    <t>4472141148</t>
   </si>
   <si>
     <t>Relatório MPS Moldagem - Lotes</t>
   </si>
   <si>
-    <t>15/05/2023</t>
-  </si>
-  <si>
-    <t>20048</t>
+    <t>4502621255</t>
   </si>
   <si>
     <t>Alteração na tela "Sequência em aberto por setor"</t>
   </si>
   <si>
-    <t>19/05/2023</t>
-  </si>
-  <si>
-    <t>18941</t>
+    <t>4504509543</t>
   </si>
   <si>
     <t>Produtivo em horas</t>
   </si>
   <si>
-    <t>19181</t>
+    <t>4427240708</t>
   </si>
   <si>
     <t>Novo processo de OTFs de Serviços/Ferramentais - PARTE I</t>
   </si>
   <si>
-    <t>19937</t>
+    <t>4426350072</t>
   </si>
   <si>
     <t>Relatório dos itens comerciais</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>4359671237</t>
   </si>
   <si>
     <t>Criar uma Procedure a partir da tela de RECIBO DE EMBARQUE DE NFe para Ajustar as quantidades Divergentes</t>
@@ -255,13 +279,13 @@
     <t>4436570246</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>4426833392</t>
   </si>
   <si>
     <t>Apontamento Registro de Pintura - Análise</t>
   </si>
   <si>
-    <t>20087</t>
+    <t>4441057492</t>
   </si>
   <si>
     <t>Tela - Criar Ordem de Movimentação</t>
@@ -270,64 +294,94 @@
     <t>09/05/2023</t>
   </si>
   <si>
+    <t>4441069887</t>
+  </si>
+  <si>
     <t>Tela - Início</t>
   </si>
   <si>
+    <t>4441081981</t>
+  </si>
+  <si>
     <t>Tabelas Auxiliares - Operadores</t>
   </si>
   <si>
+    <t>4441102243</t>
+  </si>
+  <si>
     <t>Consulta Ordens de Movimentação</t>
   </si>
   <si>
+    <t>4378090999</t>
+  </si>
+  <si>
     <t>Tela de consulta de material</t>
   </si>
   <si>
     <t>27/04/2023</t>
   </si>
   <si>
+    <t>4378094369</t>
+  </si>
+  <si>
     <t>Tela de inventário</t>
   </si>
   <si>
     <t>4436570652</t>
   </si>
   <si>
-    <t>19991</t>
+    <t>4426371697</t>
   </si>
   <si>
     <t>Previsão de OC Atualizadas.</t>
   </si>
   <si>
-    <t>20069</t>
+    <t>10/05/2023</t>
+  </si>
+  <si>
+    <t>4426438124</t>
   </si>
   <si>
     <t>Erro envio OC novo Outlook</t>
   </si>
   <si>
-    <t>20125</t>
+    <t>4427215535</t>
   </si>
   <si>
     <t>Cópia Para outro CPP - MRP</t>
   </si>
   <si>
+    <t>4378067146</t>
+  </si>
+  <si>
     <t>Construir Tema</t>
   </si>
   <si>
+    <t>4378086555</t>
+  </si>
+  <si>
     <t>Consolidar Tabelas</t>
   </si>
   <si>
-    <t>19908</t>
+    <t>4472008549</t>
   </si>
   <si>
     <t>Criar estrutura de tabelas</t>
   </si>
   <si>
+    <t>4472013448</t>
+  </si>
+  <si>
     <t>Criar Tema e menu principal</t>
   </si>
   <si>
+    <t>4472056884</t>
+  </si>
+  <si>
     <t>Consultar Método</t>
   </si>
   <si>
-    <t>17403</t>
+    <t>4427022824</t>
   </si>
   <si>
     <t>Vida útil dos modelos</t>
@@ -339,7 +393,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-10</t>
+    <t>Mar/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -981,7 +1035,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -990,7 +1044,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -998,7 +1052,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1010,10 +1064,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1025,10 +1079,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1037,80 +1091,80 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1119,10 +1173,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1131,15 +1185,15 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1151,42 +1205,42 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1198,10 +1252,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1213,10 +1267,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1225,46 +1279,46 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
@@ -1272,15 +1326,15 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1292,10 +1346,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1307,10 +1361,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1319,15 +1373,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1339,10 +1393,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1354,10 +1408,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1366,15 +1420,15 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1386,10 +1440,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1401,10 +1455,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1413,15 +1467,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1433,10 +1487,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1448,10 +1502,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1460,15 +1514,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1480,10 +1534,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1495,10 +1549,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1507,15 +1561,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1527,10 +1581,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1545,7 +1599,7 @@
         <v>66</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1557,12 +1611,12 @@
         <v>27</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1574,10 +1628,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1589,10 +1643,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1604,12 +1658,12 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1621,10 +1675,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1636,10 +1690,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1651,12 +1705,12 @@
         <v>27</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1668,10 +1722,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1683,10 +1737,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1695,15 +1749,15 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1715,10 +1769,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1730,7 +1784,7 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>24</v>
@@ -1742,15 +1796,15 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1762,10 +1816,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1777,7 +1831,7 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
@@ -1789,33 +1843,33 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1824,10 +1878,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1836,15 +1890,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1856,10 +1910,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1871,7 +1925,7 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>24</v>
@@ -1883,15 +1937,15 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1903,10 +1957,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1918,10 +1972,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1930,15 +1984,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1950,10 +2004,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1965,10 +2019,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1977,15 +2031,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1997,10 +2051,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2012,10 +2066,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2024,15 +2078,15 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2044,10 +2098,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2059,7 +2113,7 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2071,15 +2125,15 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2091,10 +2145,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2106,10 +2160,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2118,15 +2172,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>38</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2138,10 +2192,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2153,10 +2207,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2165,33 +2219,33 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>21</v>
@@ -2200,10 +2254,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2212,15 +2266,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2232,10 +2286,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2247,10 +2301,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2259,15 +2313,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2279,10 +2333,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2294,10 +2348,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2306,15 +2360,15 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2326,10 +2380,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2341,10 +2395,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2353,15 +2407,15 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2373,10 +2427,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2388,10 +2442,10 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>25</v>
@@ -2400,15 +2454,15 @@
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2420,10 +2474,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2435,10 +2489,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2447,15 +2501,15 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2467,10 +2521,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2485,7 +2539,7 @@
         <v>66</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2497,12 +2551,12 @@
         <v>27</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2514,10 +2568,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2532,7 +2586,7 @@
         <v>66</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2544,12 +2598,12 @@
         <v>27</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2561,10 +2615,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2579,7 +2633,7 @@
         <v>66</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2591,12 +2645,12 @@
         <v>27</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2608,10 +2662,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2623,7 +2677,7 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>24</v>
@@ -2635,10 +2689,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2654,23 +2708,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2678,16 +2732,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2698,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>15.76</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2706,7 +2760,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2719,7 +2773,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2727,7 +2781,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2758,12 +2812,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B2">
         <v>37</v>
@@ -2777,7 +2831,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2787,25 +2841,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2822,13 +2876,13 @@
         <v>34</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2840,21 +2894,21 @@
         <v>37</v>
       </c>
       <c r="P10" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="Q10">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2866,19 +2920,19 @@
         <v>37</v>
       </c>
       <c r="M11" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="Q11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="7:17" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G12" t="s">
         <v>20</v>
       </c>
@@ -2886,53 +2940,41 @@
         <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q12">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="7:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q13">
-        <v>6</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2940,7 +2982,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2948,7 +2990,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2956,7 +2998,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2964,10 +3006,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2975,7 +3017,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2983,139 +3025,139 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>118</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>48</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>59</v>
